--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/189.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/189.xlsx
@@ -426,13 +426,13 @@
         <v>-3.683513385271962</v>
       </c>
       <c r="E2">
-        <v>-8.647607741072971</v>
+        <v>-9.975193295057643</v>
       </c>
       <c r="F2">
-        <v>2.01506637727498</v>
+        <v>2.183273366259719</v>
       </c>
       <c r="G2">
-        <v>-8.286346293647204</v>
+        <v>-11.22968612170243</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.562372131645081</v>
       </c>
       <c r="E3">
-        <v>-9.755974396820328</v>
+        <v>-7.610750218380734</v>
       </c>
       <c r="F3">
-        <v>1.813896133366284</v>
+        <v>2.619144075718795</v>
       </c>
       <c r="G3">
-        <v>-9.191975820824691</v>
+        <v>-9.343588874886693</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.401617144863449</v>
       </c>
       <c r="E4">
-        <v>-9.023421270495525</v>
+        <v>-9.765103800419793</v>
       </c>
       <c r="F4">
-        <v>2.00553405136995</v>
+        <v>2.938911720811089</v>
       </c>
       <c r="G4">
-        <v>-8.773565901752823</v>
+        <v>-8.917114466881161</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.225687518565651</v>
       </c>
       <c r="E5">
-        <v>-10.61057442612586</v>
+        <v>-11.25222296522068</v>
       </c>
       <c r="F5">
-        <v>2.253072037070882</v>
+        <v>3.069660897483854</v>
       </c>
       <c r="G5">
-        <v>-8.651439876809109</v>
+        <v>-9.062768538972476</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.042436268729347</v>
       </c>
       <c r="E6">
-        <v>-11.48034937183109</v>
+        <v>-10.50457190655431</v>
       </c>
       <c r="F6">
-        <v>2.249652815999448</v>
+        <v>2.830641665902071</v>
       </c>
       <c r="G6">
-        <v>-8.624885991038616</v>
+        <v>-8.428712994018023</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.865633624834292</v>
       </c>
       <c r="E7">
-        <v>-11.13354071842766</v>
+        <v>-11.67162305696707</v>
       </c>
       <c r="F7">
-        <v>2.480620486707137</v>
+        <v>2.755433055683767</v>
       </c>
       <c r="G7">
-        <v>-7.280668769727403</v>
+        <v>-7.547379560553247</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.707004052989455</v>
       </c>
       <c r="E8">
-        <v>-12.44113758814247</v>
+        <v>-13.43787283112675</v>
       </c>
       <c r="F8">
-        <v>2.547673011460928</v>
+        <v>2.850507672905343</v>
       </c>
       <c r="G8">
-        <v>-7.388847466314168</v>
+        <v>-7.172791332784712</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.576356972755569</v>
       </c>
       <c r="E9">
-        <v>-13.0236261428011</v>
+        <v>-11.96335640948921</v>
       </c>
       <c r="F9">
-        <v>3.289084935773905</v>
+        <v>2.824089874529898</v>
       </c>
       <c r="G9">
-        <v>-6.298241207129903</v>
+        <v>-6.317276843980713</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.475028544129542</v>
       </c>
       <c r="E10">
-        <v>-13.28697502024316</v>
+        <v>-11.69366766843641</v>
       </c>
       <c r="F10">
-        <v>3.213545331019274</v>
+        <v>3.478242770313993</v>
       </c>
       <c r="G10">
-        <v>-6.214593652989138</v>
+        <v>-6.319097644027312</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.401183994063909</v>
       </c>
       <c r="E11">
-        <v>-14.09942401348529</v>
+        <v>-14.46789688654141</v>
       </c>
       <c r="F11">
-        <v>2.956715742712459</v>
+        <v>3.438129083181827</v>
       </c>
       <c r="G11">
-        <v>-5.660769179178922</v>
+        <v>-5.392379941764668</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.344851519256311</v>
       </c>
       <c r="E12">
-        <v>-14.81147220950336</v>
+        <v>-14.81912533057633</v>
       </c>
       <c r="F12">
-        <v>3.324225786331591</v>
+        <v>3.478291865197371</v>
       </c>
       <c r="G12">
-        <v>-5.156175828083208</v>
+        <v>-6.056303228574426</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.292357781844931</v>
       </c>
       <c r="E13">
-        <v>-15.73493674304353</v>
+        <v>-15.64366534941894</v>
       </c>
       <c r="F13">
-        <v>3.859689425988992</v>
+        <v>3.732242276149917</v>
       </c>
       <c r="G13">
-        <v>-4.376770781227053</v>
+        <v>-4.624449245747627</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.234279019262833</v>
       </c>
       <c r="E14">
-        <v>-16.76741070289634</v>
+        <v>-16.04900905784551</v>
       </c>
       <c r="F14">
-        <v>3.970048389000474</v>
+        <v>4.348421071493605</v>
       </c>
       <c r="G14">
-        <v>-4.967931587629169</v>
+        <v>-4.408290485306454</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.158330578297626</v>
       </c>
       <c r="E15">
-        <v>-16.99954028052953</v>
+        <v>-18.75933697922828</v>
       </c>
       <c r="F15">
-        <v>4.395096052233437</v>
+        <v>4.544539293532049</v>
       </c>
       <c r="G15">
-        <v>-4.306001249234053</v>
+        <v>-4.026862670453784</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.056213276810436</v>
       </c>
       <c r="E16">
-        <v>-18.26520800940732</v>
+        <v>-18.78246389598545</v>
       </c>
       <c r="F16">
-        <v>4.25645051786629</v>
+        <v>4.759725334792384</v>
       </c>
       <c r="G16">
-        <v>-3.166501542980293</v>
+        <v>-3.456743691499276</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.922553863404973</v>
       </c>
       <c r="E17">
-        <v>-19.14828308327308</v>
+        <v>-18.82703313716894</v>
       </c>
       <c r="F17">
-        <v>4.71223157809427</v>
+        <v>4.890940121004289</v>
       </c>
       <c r="G17">
-        <v>-3.044805888956684</v>
+        <v>-4.372301544749037</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.755132055940166</v>
       </c>
       <c r="E18">
-        <v>-21.18883158502537</v>
+        <v>-19.50184369142194</v>
       </c>
       <c r="F18">
-        <v>4.887701442407215</v>
+        <v>4.991066760096117</v>
       </c>
       <c r="G18">
-        <v>-2.791605434476605</v>
+        <v>-2.572245376498957</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.560976094461136</v>
       </c>
       <c r="E19">
-        <v>-21.74838341883515</v>
+        <v>-20.77039605824262</v>
       </c>
       <c r="F19">
-        <v>5.079238003232293</v>
+        <v>5.0227915569942</v>
       </c>
       <c r="G19">
-        <v>-2.913109076858936</v>
+        <v>-3.221499636024205</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.352555966572694</v>
       </c>
       <c r="E20">
-        <v>-20.31299754109788</v>
+        <v>-21.06714695996526</v>
       </c>
       <c r="F20">
-        <v>5.218345979726747</v>
+        <v>5.590521620972764</v>
       </c>
       <c r="G20">
-        <v>-2.285439574249737</v>
+        <v>-2.870555324497145</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.1501116607016</v>
       </c>
       <c r="E21">
-        <v>-21.87422971150831</v>
+        <v>-20.55273495506395</v>
       </c>
       <c r="F21">
-        <v>5.127453929827847</v>
+        <v>5.889124620211125</v>
       </c>
       <c r="G21">
-        <v>-2.686081795412336</v>
+        <v>-2.333763607486479</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.9789617134208165</v>
       </c>
       <c r="E22">
-        <v>-22.95791165543985</v>
+        <v>-23.08583651768253</v>
       </c>
       <c r="F22">
-        <v>5.559300442555791</v>
+        <v>5.970425747086125</v>
       </c>
       <c r="G22">
-        <v>-2.066370844279545</v>
+        <v>-2.737206550175301</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.8637085614933887</v>
       </c>
       <c r="E23">
-        <v>-23.33669586381144</v>
+        <v>-22.73087208259129</v>
       </c>
       <c r="F23">
-        <v>5.463036462191719</v>
+        <v>5.858459322570472</v>
       </c>
       <c r="G23">
-        <v>-1.611346291543338</v>
+        <v>-2.015130220422706</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.8273360753643199</v>
       </c>
       <c r="E24">
-        <v>-23.81956251877532</v>
+        <v>-23.30979219973187</v>
       </c>
       <c r="F24">
-        <v>5.533112281538084</v>
+        <v>5.532225406225438</v>
       </c>
       <c r="G24">
-        <v>-2.556007150628832</v>
+        <v>-2.681437100020739</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.8823143564477054</v>
       </c>
       <c r="E25">
-        <v>-22.72569150832652</v>
+        <v>-24.48575991546573</v>
       </c>
       <c r="F25">
-        <v>5.580829340770275</v>
+        <v>5.679418201418211</v>
       </c>
       <c r="G25">
-        <v>-2.106133806751731</v>
+        <v>-3.130482807513022</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.036938787290741</v>
       </c>
       <c r="E26">
-        <v>-23.40400710146145</v>
+        <v>-23.54241085255788</v>
       </c>
       <c r="F26">
-        <v>5.418778216678849</v>
+        <v>5.962925315870604</v>
       </c>
       <c r="G26">
-        <v>-2.008002615876654</v>
+        <v>-3.734773237523888</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.289504665367982</v>
       </c>
       <c r="E27">
-        <v>-24.13089057832865</v>
+        <v>-23.45213572321497</v>
       </c>
       <c r="F27">
-        <v>5.727952452902768</v>
+        <v>6.121479617300739</v>
       </c>
       <c r="G27">
-        <v>-2.11767767904717</v>
+        <v>-2.221867168259112</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.627701233471955</v>
       </c>
       <c r="E28">
-        <v>-25.27306229254327</v>
+        <v>-23.99374121453235</v>
       </c>
       <c r="F28">
-        <v>5.227236904736024</v>
+        <v>6.165050534446309</v>
       </c>
       <c r="G28">
-        <v>-1.069654967134551</v>
+        <v>-3.482592431069905</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.036602944944399</v>
       </c>
       <c r="E29">
-        <v>-23.36325989234043</v>
+        <v>-22.53657790529219</v>
       </c>
       <c r="F29">
-        <v>5.340766446990217</v>
+        <v>6.083899859633276</v>
       </c>
       <c r="G29">
-        <v>-2.418808211844816</v>
+        <v>-3.05272802443216</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.492845887764509</v>
       </c>
       <c r="E30">
-        <v>-22.00877067427619</v>
+        <v>-23.48540189327532</v>
       </c>
       <c r="F30">
-        <v>5.301126287926767</v>
+        <v>6.079006208354569</v>
       </c>
       <c r="G30">
-        <v>-1.822999399505563</v>
+        <v>-2.793323607611487</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.972961824312509</v>
       </c>
       <c r="E31">
-        <v>-23.18296322819905</v>
+        <v>-22.17357090036333</v>
       </c>
       <c r="F31">
-        <v>5.219476745750371</v>
+        <v>5.495394741455978</v>
       </c>
       <c r="G31">
-        <v>-1.572457313093519</v>
+        <v>-2.277951120239906</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.453771914631762</v>
       </c>
       <c r="E32">
-        <v>-21.84679621596984</v>
+        <v>-22.56973539197636</v>
       </c>
       <c r="F32">
-        <v>5.524829499600336</v>
+        <v>5.452061380197724</v>
       </c>
       <c r="G32">
-        <v>-2.391615390785243</v>
+        <v>-3.817914278197144</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.907868964202679</v>
       </c>
       <c r="E33">
-        <v>-21.86586109154213</v>
+        <v>-20.53101639372316</v>
       </c>
       <c r="F33">
-        <v>5.162959032746084</v>
+        <v>5.406316034830255</v>
       </c>
       <c r="G33">
-        <v>-3.029087418736224</v>
+        <v>-3.214590527483745</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.319143828634805</v>
       </c>
       <c r="E34">
-        <v>-22.41666391356908</v>
+        <v>-21.912422861289</v>
       </c>
       <c r="F34">
-        <v>5.472692317158153</v>
+        <v>5.789970376551377</v>
       </c>
       <c r="G34">
-        <v>-2.830752635478487</v>
+        <v>-4.053198060218687</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.673743888657845</v>
       </c>
       <c r="E35">
-        <v>-21.6034179089016</v>
+        <v>-19.96313669621328</v>
       </c>
       <c r="F35">
-        <v>5.431766188891367</v>
+        <v>5.056915668354174</v>
       </c>
       <c r="G35">
-        <v>-2.059014812091284</v>
+        <v>-3.696976739102029</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.963707569570369</v>
       </c>
       <c r="E36">
-        <v>-22.34559857096671</v>
+        <v>-20.7486548545318</v>
       </c>
       <c r="F36">
-        <v>5.091487968488217</v>
+        <v>5.156039821601529</v>
       </c>
       <c r="G36">
-        <v>-3.709838208522097</v>
+        <v>-2.535816133384817</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.19389414302865</v>
       </c>
       <c r="E37">
-        <v>-20.74467885435307</v>
+        <v>-19.43825485940624</v>
       </c>
       <c r="F37">
-        <v>4.978907066077372</v>
+        <v>5.332599275584295</v>
       </c>
       <c r="G37">
-        <v>-2.544906891435656</v>
+        <v>-4.683280950526015</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.369403074374502</v>
       </c>
       <c r="E38">
-        <v>-18.89599726783176</v>
+        <v>-20.35129031730674</v>
       </c>
       <c r="F38">
-        <v>5.060165432892656</v>
+        <v>5.52592859150565</v>
       </c>
       <c r="G38">
-        <v>-2.817844818420869</v>
+        <v>-4.236320886723473</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.5054370452421</v>
       </c>
       <c r="E39">
-        <v>-18.36885572249488</v>
+        <v>-19.52943115507667</v>
       </c>
       <c r="F39">
-        <v>5.138216795229173</v>
+        <v>5.395762218609767</v>
       </c>
       <c r="G39">
-        <v>-3.747095088021055</v>
+        <v>-3.848159422243926</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.621075786668307</v>
       </c>
       <c r="E40">
-        <v>-17.50874906879603</v>
+        <v>-17.94085153013392</v>
       </c>
       <c r="F40">
-        <v>4.885829502015166</v>
+        <v>5.267504211341988</v>
       </c>
       <c r="G40">
-        <v>-4.124017250394776</v>
+        <v>-3.927781353008938</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.729127084329503</v>
       </c>
       <c r="E41">
-        <v>-18.37777228781598</v>
+        <v>-18.65850597697349</v>
       </c>
       <c r="F41">
-        <v>5.401536410377459</v>
+        <v>5.359580873265637</v>
       </c>
       <c r="G41">
-        <v>-3.32358692881871</v>
+        <v>-3.775287693833489</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.847835464370963</v>
       </c>
       <c r="E42">
-        <v>-18.61430807065863</v>
+        <v>-16.85255507118856</v>
       </c>
       <c r="F42">
-        <v>4.927224407232922</v>
+        <v>5.519034719655743</v>
       </c>
       <c r="G42">
-        <v>-3.527354317306391</v>
+        <v>-4.29951920106816</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.988008317177623</v>
       </c>
       <c r="E43">
-        <v>-17.33437112018266</v>
+        <v>-17.59089558729517</v>
       </c>
       <c r="F43">
-        <v>5.196351471973125</v>
+        <v>5.72147509570862</v>
       </c>
       <c r="G43">
-        <v>-3.918617762956235</v>
+        <v>-4.125281878790778</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.152591077585277</v>
       </c>
       <c r="E44">
-        <v>-17.97155005543192</v>
+        <v>-16.1099306186707</v>
       </c>
       <c r="F44">
-        <v>5.384023790364529</v>
+        <v>5.742080693374404</v>
       </c>
       <c r="G44">
-        <v>-3.723596835783308</v>
+        <v>-4.30224378004698</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.344047130909926</v>
       </c>
       <c r="E45">
-        <v>-16.33985482946215</v>
+        <v>-15.75567262552465</v>
       </c>
       <c r="F45">
-        <v>5.284871130410696</v>
+        <v>5.636447508814593</v>
       </c>
       <c r="G45">
-        <v>-3.74462211050322</v>
+        <v>-3.947995544071727</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.555159160781939</v>
       </c>
       <c r="E46">
-        <v>-14.73377718095376</v>
+        <v>-13.87107118317451</v>
       </c>
       <c r="F46">
-        <v>5.249023947014725</v>
+        <v>5.281068652507726</v>
       </c>
       <c r="G46">
-        <v>-4.720392166021245</v>
+        <v>-3.422638451353704</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.777535621613981</v>
       </c>
       <c r="E47">
-        <v>-14.8635089043255</v>
+        <v>-16.03915962687883</v>
       </c>
       <c r="F47">
-        <v>5.550697752023123</v>
+        <v>5.380819953297595</v>
       </c>
       <c r="G47">
-        <v>-3.932240657850336</v>
+        <v>-5.150832607582824</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.003407012104517</v>
       </c>
       <c r="E48">
-        <v>-13.58949519785157</v>
+        <v>-14.58241746572139</v>
       </c>
       <c r="F48">
-        <v>5.57322596867025</v>
+        <v>5.083203602844553</v>
       </c>
       <c r="G48">
-        <v>-4.217089927685847</v>
+        <v>-4.581749829382107</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.218332140970257</v>
       </c>
       <c r="E49">
-        <v>-13.27192237264166</v>
+        <v>-13.41240469330761</v>
       </c>
       <c r="F49">
-        <v>5.085032783176885</v>
+        <v>5.793012675614936</v>
       </c>
       <c r="G49">
-        <v>-3.983269406792662</v>
+        <v>-5.258600796522719</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.415460087950126</v>
       </c>
       <c r="E50">
-        <v>-13.5409861842814</v>
+        <v>-12.99639190011897</v>
       </c>
       <c r="F50">
-        <v>5.505910548734496</v>
+        <v>5.30221904500842</v>
       </c>
       <c r="G50">
-        <v>-3.927923706467126</v>
+        <v>-4.006377014656775</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.590232410134098</v>
       </c>
       <c r="E51">
-        <v>-12.47877373562022</v>
+        <v>-13.06149324245324</v>
       </c>
       <c r="F51">
-        <v>5.097496548731394</v>
+        <v>5.747896061495897</v>
       </c>
       <c r="G51">
-        <v>-3.999620191211122</v>
+        <v>-4.66117974850584</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.737045885613436</v>
       </c>
       <c r="E52">
-        <v>-11.12762653137364</v>
+        <v>-12.95629679125505</v>
       </c>
       <c r="F52">
-        <v>5.462170175055974</v>
+        <v>5.365418413269947</v>
       </c>
       <c r="G52">
-        <v>-3.744632042139838</v>
+        <v>-4.82039050458047</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.85824067470256</v>
       </c>
       <c r="E53">
-        <v>-11.06660081564628</v>
+        <v>-11.67159135764901</v>
       </c>
       <c r="F53">
-        <v>5.402679846048406</v>
+        <v>5.043941949494894</v>
       </c>
       <c r="G53">
-        <v>-3.547204348359861</v>
+        <v>-4.525265301391062</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.954658871366518</v>
       </c>
       <c r="E54">
-        <v>-9.926104636814497</v>
+        <v>-11.28979118558832</v>
       </c>
       <c r="F54">
-        <v>5.646253815842993</v>
+        <v>5.236922850114852</v>
       </c>
       <c r="G54">
-        <v>-5.182342380025607</v>
+        <v>-4.543781182592205</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.030011025982482</v>
       </c>
       <c r="E55">
-        <v>-10.36215139901308</v>
+        <v>-10.76532143991597</v>
       </c>
       <c r="F55">
-        <v>5.207027233549102</v>
+        <v>5.137689421159331</v>
       </c>
       <c r="G55">
-        <v>-5.144198274322124</v>
+        <v>-4.132214161150012</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.09119388048048</v>
       </c>
       <c r="E56">
-        <v>-9.893001491818426</v>
+        <v>-10.58551385096741</v>
       </c>
       <c r="F56">
-        <v>5.671841752318748</v>
+        <v>5.031752165063756</v>
       </c>
       <c r="G56">
-        <v>-4.503667302292857</v>
+        <v>-4.961621687831318</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.138230483400108</v>
       </c>
       <c r="E57">
-        <v>-8.996232312553472</v>
+        <v>-9.964361185231295</v>
       </c>
       <c r="F57">
-        <v>5.359026576195234</v>
+        <v>5.287401892463569</v>
       </c>
       <c r="G57">
-        <v>-5.237966166176442</v>
+        <v>-4.589708380858515</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.17359545151397</v>
       </c>
       <c r="E58">
-        <v>-10.29699118651671</v>
+        <v>-9.525896217912621</v>
       </c>
       <c r="F58">
-        <v>5.073291187519818</v>
+        <v>5.014850855534187</v>
       </c>
       <c r="G58">
-        <v>-4.515591887325312</v>
+        <v>-5.170007287346283</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.199380510357795</v>
       </c>
       <c r="E59">
-        <v>-9.506392080361584</v>
+        <v>-9.524265967269859</v>
       </c>
       <c r="F59">
-        <v>5.347384754010838</v>
+        <v>5.536553674492334</v>
       </c>
       <c r="G59">
-        <v>-5.315274025609503</v>
+        <v>-3.694487208856497</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.210540676259082</v>
       </c>
       <c r="E60">
-        <v>-8.309620555036485</v>
+        <v>-8.420491184166279</v>
       </c>
       <c r="F60">
-        <v>5.293450065354632</v>
+        <v>5.117926355040563</v>
       </c>
       <c r="G60">
-        <v>-5.331717505303063</v>
+        <v>-4.068105446782025</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.204521617932468</v>
       </c>
       <c r="E61">
-        <v>-7.500771698630452</v>
+        <v>-9.854196998046699</v>
       </c>
       <c r="F61">
-        <v>4.933334344654687</v>
+        <v>5.287584018643845</v>
       </c>
       <c r="G61">
-        <v>-5.536732969459049</v>
+        <v>-5.477364956303298</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.176880640673295</v>
       </c>
       <c r="E62">
-        <v>-7.982198298859895</v>
+        <v>-7.711766888069837</v>
       </c>
       <c r="F62">
-        <v>5.215178567895868</v>
+        <v>5.404342737259618</v>
       </c>
       <c r="G62">
-        <v>-4.623399802811678</v>
+        <v>-4.844640250655632</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.121760221951803</v>
       </c>
       <c r="E63">
-        <v>-6.556616567349236</v>
+        <v>-8.034497645174481</v>
       </c>
       <c r="F63">
-        <v>5.259878667359147</v>
+        <v>5.247291372743234</v>
       </c>
       <c r="G63">
-        <v>-4.521133740558051</v>
+        <v>-4.588897297201393</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.038185769507161</v>
       </c>
       <c r="E64">
-        <v>-6.672065483700784</v>
+        <v>-6.221740442956021</v>
       </c>
       <c r="F64">
-        <v>5.052807535209523</v>
+        <v>4.821021088543552</v>
       </c>
       <c r="G64">
-        <v>-5.406234574846517</v>
+        <v>-4.538984202105802</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.921924185544718</v>
       </c>
       <c r="E65">
-        <v>-7.011388569569532</v>
+        <v>-6.297954660505114</v>
       </c>
       <c r="F65">
-        <v>4.997400000051959</v>
+        <v>4.879322054408624</v>
       </c>
       <c r="G65">
-        <v>-5.92977748860902</v>
+        <v>-5.05173473741028</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.769810202729053</v>
       </c>
       <c r="E66">
-        <v>-7.019313399082955</v>
+        <v>-7.44700965521139</v>
       </c>
       <c r="F66">
-        <v>5.139751406261234</v>
+        <v>4.805491268336753</v>
       </c>
       <c r="G66">
-        <v>-4.998706418962234</v>
+        <v>-5.73949726264833</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.585500162420234</v>
       </c>
       <c r="E67">
-        <v>-6.218063322061793</v>
+        <v>-6.834556188044012</v>
       </c>
       <c r="F67">
-        <v>4.820317923117098</v>
+        <v>4.782969386513289</v>
       </c>
       <c r="G67">
-        <v>-5.46023288313757</v>
+        <v>-5.494897605479278</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.366518051806175</v>
       </c>
       <c r="E68">
-        <v>-4.950978180819596</v>
+        <v>-7.140712730280582</v>
       </c>
       <c r="F68">
-        <v>4.684440706690139</v>
+        <v>5.037208031942445</v>
       </c>
       <c r="G68">
-        <v>-6.208061946640156</v>
+        <v>-5.235228345015464</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.114030717846791</v>
       </c>
       <c r="E69">
-        <v>-6.278138058247547</v>
+        <v>-6.572212631831653</v>
       </c>
       <c r="F69">
-        <v>4.330867275126875</v>
+        <v>4.519534160833175</v>
       </c>
       <c r="G69">
-        <v>-5.141808060442771</v>
+        <v>-4.891222936938717</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.832932499552084</v>
       </c>
       <c r="E70">
-        <v>-5.51907977355585</v>
+        <v>-7.727055016319732</v>
       </c>
       <c r="F70">
-        <v>3.865297328635563</v>
+        <v>4.673934401647114</v>
       </c>
       <c r="G70">
-        <v>-5.621264439258799</v>
+        <v>-5.591469529405359</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.524649886619954</v>
       </c>
       <c r="E71">
-        <v>-6.543909669283713</v>
+        <v>-6.508297749687394</v>
       </c>
       <c r="F71">
-        <v>4.711081807599661</v>
+        <v>4.168125655256317</v>
       </c>
       <c r="G71">
-        <v>-5.493636287628816</v>
+        <v>-4.826379281461012</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.196918821827186</v>
       </c>
       <c r="E72">
-        <v>-5.295341458258881</v>
+        <v>-6.405632715459499</v>
       </c>
       <c r="F72">
-        <v>3.914346284542638</v>
+        <v>4.382551517677241</v>
       </c>
       <c r="G72">
-        <v>-4.725308326147062</v>
+        <v>-4.950554534093535</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.855540166967805</v>
       </c>
       <c r="E73">
-        <v>-6.031825300022342</v>
+        <v>-6.378362244985308</v>
       </c>
       <c r="F73">
-        <v>3.945944384967486</v>
+        <v>4.899653670951037</v>
       </c>
       <c r="G73">
-        <v>-4.530760806986252</v>
+        <v>-4.994528510491675</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.501771658854639</v>
       </c>
       <c r="E74">
-        <v>-6.475158376899262</v>
+        <v>-7.62160497057712</v>
       </c>
       <c r="F74">
-        <v>3.910589734111216</v>
+        <v>3.925666614426199</v>
       </c>
       <c r="G74">
-        <v>-4.69765864980307</v>
+        <v>-4.888941971062159</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.146512034335691</v>
       </c>
       <c r="E75">
-        <v>-5.858756080397196</v>
+        <v>-6.333779418379794</v>
       </c>
       <c r="F75">
-        <v>4.010160492426724</v>
+        <v>3.829239512352837</v>
       </c>
       <c r="G75">
-        <v>-5.258047935417661</v>
+        <v>-4.743469978975504</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.792157901800871</v>
       </c>
       <c r="E76">
-        <v>-6.348270535204339</v>
+        <v>-7.01531928500819</v>
       </c>
       <c r="F76">
-        <v>3.683369111599456</v>
+        <v>3.906221873196433</v>
       </c>
       <c r="G76">
-        <v>-3.868592109312308</v>
+        <v>-5.514366923795732</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.440435088409933</v>
       </c>
       <c r="E77">
-        <v>-7.526584000474173</v>
+        <v>-8.836603603783093</v>
       </c>
       <c r="F77">
-        <v>3.850887188510979</v>
+        <v>4.509084869203106</v>
       </c>
       <c r="G77">
-        <v>-3.96247255971496</v>
+        <v>-3.938348614370291</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.097636173535177</v>
       </c>
       <c r="E78">
-        <v>-7.332416620447291</v>
+        <v>-8.989113551413414</v>
       </c>
       <c r="F78">
-        <v>3.727530751051485</v>
+        <v>3.866508863660874</v>
       </c>
       <c r="G78">
-        <v>-4.255571709034335</v>
+        <v>-3.63560253534948</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.762477881826865</v>
       </c>
       <c r="E79">
-        <v>-6.673084390352511</v>
+        <v>-8.81507070987662</v>
       </c>
       <c r="F79">
-        <v>3.842046942090996</v>
+        <v>3.322578732179534</v>
       </c>
       <c r="G79">
-        <v>-3.683893463130829</v>
+        <v>-3.93326692696751</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.440320225562122</v>
       </c>
       <c r="E80">
-        <v>-8.238147649773424</v>
+        <v>-10.72833286422131</v>
       </c>
       <c r="F80">
-        <v>3.738661036225194</v>
+        <v>4.308087249239193</v>
       </c>
       <c r="G80">
-        <v>-3.718799855296905</v>
+        <v>-3.107851918206564</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.134240017642839</v>
       </c>
       <c r="E81">
-        <v>-10.17810515839334</v>
+        <v>-9.573644447849498</v>
       </c>
       <c r="F81">
-        <v>3.669405576543026</v>
+        <v>3.756537908598674</v>
       </c>
       <c r="G81">
-        <v>-2.886376421629322</v>
+        <v>-2.888670629688037</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.846571732945258</v>
       </c>
       <c r="E82">
-        <v>-8.33379354928943</v>
+        <v>-10.48499984189316</v>
       </c>
       <c r="F82">
-        <v>3.477485758886413</v>
+        <v>3.54153557722453</v>
       </c>
       <c r="G82">
-        <v>-3.356675831483726</v>
+        <v>-2.596276626568527</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.588407541976988</v>
       </c>
       <c r="E83">
-        <v>-10.07195319917954</v>
+        <v>-11.39486083951429</v>
       </c>
       <c r="F83">
-        <v>3.663187947119011</v>
+        <v>3.164524881818677</v>
       </c>
       <c r="G83">
-        <v>-2.204953591098976</v>
+        <v>-2.428951723377143</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.366587579247658</v>
       </c>
       <c r="E84">
-        <v>-12.18581769511601</v>
+        <v>-11.5545710608168</v>
       </c>
       <c r="F84">
-        <v>3.282479298400607</v>
+        <v>3.734628920964485</v>
       </c>
       <c r="G84">
-        <v>-2.216192893204802</v>
+        <v>-2.410396115629528</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.193163491343496</v>
       </c>
       <c r="E85">
-        <v>-12.79675412349082</v>
+        <v>-13.45902080474257</v>
       </c>
       <c r="F85">
-        <v>3.289794436024022</v>
+        <v>4.007780182435819</v>
       </c>
       <c r="G85">
-        <v>-1.919428969973454</v>
+        <v>-2.903627674434464</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.079109435396252</v>
       </c>
       <c r="E86">
-        <v>-12.55989681899363</v>
+        <v>-14.45739535531762</v>
       </c>
       <c r="F86">
-        <v>3.504258307386916</v>
+        <v>3.02971666688464</v>
       </c>
       <c r="G86">
-        <v>-1.543082842523566</v>
+        <v>-1.514142053419258</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.036835825143229</v>
       </c>
       <c r="E87">
-        <v>-15.13343765450071</v>
+        <v>-16.1701502660247</v>
       </c>
       <c r="F87">
-        <v>2.666089870170166</v>
+        <v>3.073829211453291</v>
       </c>
       <c r="G87">
-        <v>-1.286184508676122</v>
+        <v>-1.237446657246972</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.079638121204746</v>
       </c>
       <c r="E88">
-        <v>-16.04850186875665</v>
+        <v>-18.06589628290773</v>
       </c>
       <c r="F88">
-        <v>3.172573275280941</v>
+        <v>2.495597593549448</v>
       </c>
       <c r="G88">
-        <v>-1.724891382449261</v>
+        <v>-1.107809004474651</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.213078696873363</v>
       </c>
       <c r="E89">
-        <v>-18.15153878334079</v>
+        <v>-19.26974128463281</v>
       </c>
       <c r="F89">
-        <v>3.023554467167666</v>
+        <v>2.576854376658815</v>
       </c>
       <c r="G89">
-        <v>-1.245183402172248</v>
+        <v>-1.692037528517534</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.444428174214586</v>
       </c>
       <c r="E90">
-        <v>-18.16847527612947</v>
+        <v>-19.53722918731788</v>
       </c>
       <c r="F90">
-        <v>2.695740012319023</v>
+        <v>2.838213363883787</v>
       </c>
       <c r="G90">
-        <v>-1.435758266685934</v>
+        <v>-1.444607354912405</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.774550736212736</v>
       </c>
       <c r="E91">
-        <v>-20.86711520609845</v>
+        <v>-21.93549996483209</v>
       </c>
       <c r="F91">
-        <v>2.502531058047242</v>
+        <v>2.544066913091472</v>
       </c>
       <c r="G91">
-        <v>-1.069592066769305</v>
+        <v>-0.9553153452992026</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.198812345927439</v>
       </c>
       <c r="E92">
-        <v>-23.52548341671721</v>
+        <v>-24.65945859297794</v>
       </c>
       <c r="F92">
-        <v>1.917487921001094</v>
+        <v>2.314256931407969</v>
       </c>
       <c r="G92">
-        <v>-0.8689001750876068</v>
+        <v>-0.7020155744529463</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.713654960562552</v>
       </c>
       <c r="E93">
-        <v>-24.94507850558973</v>
+        <v>-25.50570811621333</v>
       </c>
       <c r="F93">
-        <v>1.547678336392744</v>
+        <v>1.944040334379352</v>
       </c>
       <c r="G93">
-        <v>-0.3058823163148345</v>
+        <v>-0.6529102524689367</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.300016812777932</v>
       </c>
       <c r="E94">
-        <v>-26.44500872335832</v>
+        <v>-28.23827990192177</v>
       </c>
       <c r="F94">
-        <v>1.185435698648364</v>
+        <v>1.652272609872027</v>
       </c>
       <c r="G94">
-        <v>-0.9574274733532576</v>
+        <v>0.07223164245302412</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.94523242703718</v>
       </c>
       <c r="E95">
-        <v>-27.9495987408808</v>
+        <v>-30.80556691482426</v>
       </c>
       <c r="F95">
-        <v>1.352592690611166</v>
+        <v>1.260276889094285</v>
       </c>
       <c r="G95">
-        <v>-0.8012226926282858</v>
+        <v>-1.424720907858003</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.633881363729236</v>
       </c>
       <c r="E96">
-        <v>-30.54067609198259</v>
+        <v>-31.04210722614091</v>
       </c>
       <c r="F96">
-        <v>1.375450318088704</v>
+        <v>1.291151235915778</v>
       </c>
       <c r="G96">
-        <v>-0.1528093116700134</v>
+        <v>-0.7853386951308627</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.334702537898823</v>
       </c>
       <c r="E97">
-        <v>-33.34279844573783</v>
+        <v>-34.56196327503087</v>
       </c>
       <c r="F97">
-        <v>0.9346511158207808</v>
+        <v>1.382352108468189</v>
       </c>
       <c r="G97">
-        <v>-2.156043591301783</v>
+        <v>-1.065304910295948</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.042495346129945</v>
       </c>
       <c r="E98">
-        <v>-35.71857176438193</v>
+        <v>-36.19990326665722</v>
       </c>
       <c r="F98">
-        <v>0.8771926815027221</v>
+        <v>1.632367010220868</v>
       </c>
       <c r="G98">
-        <v>-0.999828940620243</v>
+        <v>-1.233702430242056</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.721358877512079</v>
       </c>
       <c r="E99">
-        <v>-37.26612567905219</v>
+        <v>-39.71140201676602</v>
       </c>
       <c r="F99">
-        <v>0.4271596818948293</v>
+        <v>0.2090501195145931</v>
       </c>
       <c r="G99">
-        <v>-1.219480326605347</v>
+        <v>-0.8297761479044998</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.382674215099204</v>
       </c>
       <c r="E100">
-        <v>-39.74786302523878</v>
+        <v>-41.25844647811041</v>
       </c>
       <c r="F100">
-        <v>0.174458023056607</v>
+        <v>0.8992457863752165</v>
       </c>
       <c r="G100">
-        <v>-1.128052990447294</v>
+        <v>-1.513519670857874</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.983493139734584</v>
       </c>
       <c r="E101">
-        <v>-42.73426936449917</v>
+        <v>-43.06787525193323</v>
       </c>
       <c r="F101">
-        <v>0.1890146559783687</v>
+        <v>0.5070845683293118</v>
       </c>
       <c r="G101">
-        <v>-1.983670106163011</v>
+        <v>-2.049890948585053</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.580368072575775</v>
       </c>
       <c r="E102">
-        <v>-44.50415323905001</v>
+        <v>-45.84369170017793</v>
       </c>
       <c r="F102">
-        <v>-0.1966644537556422</v>
+        <v>-0.5847880135701339</v>
       </c>
       <c r="G102">
-        <v>-2.098767842926853</v>
+        <v>-2.467807596371569</v>
       </c>
     </row>
   </sheetData>
